--- a/training/performance/recap_scores.xlsx
+++ b/training/performance/recap_scores.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,38 +509,82 @@
           <t>CV_Var</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>BEM_Ratio_C</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Best_BEM_Ratio_AB</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BASELINE_BEM</t>
+          <t>GM_0_f_D0_A</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM_0_f_D0_A</t>
+          <t>GM_1_f_D0_A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.52</v>
+        <v>3.88</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -548,7 +592,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -578,24 +622,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>459.9</v>
+        <v>59.64</v>
       </c>
       <c r="O3" t="n">
-        <v>64.2</v>
-      </c>
+        <v>11.73</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_A</t>
+          <t>GM_2_f_D0_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.88</v>
+        <v>0.48</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -603,7 +649,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -633,32 +679,34 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>59.64</v>
+        <v>467.35</v>
       </c>
       <c r="O4" t="n">
-        <v>11.73</v>
-      </c>
+        <v>111.04</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM_2_f_D0_A</t>
+          <t>GV_1_f_D0_A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.48</v>
+        <v>2.28</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>GV</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -688,28 +736,30 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>467.35</v>
+        <v>104.85</v>
       </c>
       <c r="O5" t="n">
-        <v>111.04</v>
-      </c>
+        <v>15.89</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GV_1_f_D0_A</t>
+          <t>GM_1_v_D0_A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.28</v>
+        <v>4.24</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GV</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -717,7 +767,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -733,13 +783,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -747,20 +797,22 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>104.85</v>
+        <v>73.41</v>
       </c>
       <c r="O6" t="n">
-        <v>15.89</v>
-      </c>
+        <v>14.2</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_A</t>
+          <t>GM_1_f_D0_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.24</v>
+        <v>3.01</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -772,7 +824,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>f</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -784,17 +836,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -802,20 +854,22 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>73.41</v>
+        <v>7.15</v>
       </c>
       <c r="O7" t="n">
-        <v>14.2</v>
-      </c>
+        <v>0.31</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_B</t>
+          <t>GM_1_v_D0_B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.01</v>
+        <v>5.09</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -827,7 +881,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -843,13 +897,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -857,20 +911,22 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>7.15</v>
+        <v>8.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0.31</v>
-      </c>
+        <v>0.84</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_B</t>
+          <t>GM_0_f_DM16_A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.09</v>
+        <v>0.52</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -878,54 +934,60 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>v</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="N9" t="n">
-        <v>8.85</v>
+        <v>577.41</v>
       </c>
       <c r="O9" t="n">
-        <v>0.84</v>
-      </c>
+        <v>77.52</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GM_0_f_DM16_A</t>
+          <t>GM_1_f_DM32_A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.52</v>
+        <v>2.52</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -933,7 +995,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -949,7 +1011,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -967,24 +1029,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>577.41</v>
+        <v>76.06</v>
       </c>
       <c r="O10" t="n">
-        <v>77.52</v>
-      </c>
+        <v>11.63</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GM_1_f_DM32_A</t>
+          <t>GM_2_f_DV32_A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.52</v>
+        <v>0.46</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -992,7 +1056,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1004,7 +1068,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1026,24 +1090,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>76.06</v>
+        <v>562.58</v>
       </c>
       <c r="O11" t="n">
-        <v>11.63</v>
-      </c>
+        <v>97.73</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GM_2_f_DV32_A</t>
+          <t>GM_1_v_DV32_A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.46</v>
+        <v>6.86</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1051,11 +1117,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1075,34 +1141,36 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>562.58</v>
+        <v>81.36</v>
       </c>
       <c r="O12" t="n">
-        <v>97.73</v>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GM_1_v_DV32_A</t>
+          <t>GM_2_v_DM16_A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.86</v>
+        <v>0.6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1110,7 +1178,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1122,11 +1190,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1134,46 +1202,50 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>81.36</v>
+        <v>566.85</v>
       </c>
       <c r="O13" t="n">
-        <v>8.9</v>
-      </c>
+        <v>57.54</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GM_2_v_DM16_A</t>
+          <t>GM_2+_f_DM16_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>f</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1193,13 +1265,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1207,20 +1279,22 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>566.85</v>
+        <v>411.05</v>
       </c>
       <c r="O14" t="n">
-        <v>57.54</v>
-      </c>
+        <v>56.67</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GM_2+_f_DM16_A</t>
+          <t>GM_2+_v_DV16_A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1234,7 +1308,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1242,7 +1316,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1254,85 +1328,53 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>411.05</v>
+        <v>285.59</v>
       </c>
       <c r="O15" t="n">
-        <v>56.67</v>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GM_2+_v_DV16_A</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2+</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>v</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+          <t>BASELINE_BEM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>16</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>285.59</v>
-      </c>
-      <c r="O16" t="n">
-        <v>8.199999999999999</v>
+      <c r="Q16" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1379,286 +1421,286 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BASELINE_BEM</t>
+          <t>GM_0_f_D0_A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.3797</v>
+        <v>67.8278</v>
       </c>
       <c r="C2" t="n">
-        <v>17.44</v>
+        <v>27.74</v>
       </c>
       <c r="D2" t="n">
-        <v>9.94</v>
+        <v>20.07</v>
       </c>
       <c r="E2" t="n">
-        <v>13.8425</v>
+        <v>19.7755</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM_0_f_D0_A</t>
+          <t>GM_1_f_D0_A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.8278</v>
+        <v>12.067</v>
       </c>
       <c r="C3" t="n">
-        <v>27.74</v>
+        <v>6.51</v>
       </c>
       <c r="D3" t="n">
-        <v>20.07</v>
+        <v>4.93</v>
       </c>
       <c r="E3" t="n">
-        <v>19.7755</v>
+        <v>2.4735</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_A</t>
+          <t>GM_2_f_D0_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.067</v>
+        <v>77.28360000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>6.51</v>
+        <v>32.09</v>
       </c>
       <c r="D4" t="n">
-        <v>4.93</v>
+        <v>22.56</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4735</v>
+        <v>22.4027</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM_2_f_D0_A</t>
+          <t>GV_1_f_D0_A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.28360000000001</v>
+        <v>25.8915</v>
       </c>
       <c r="C5" t="n">
-        <v>32.09</v>
+        <v>113.31</v>
       </c>
       <c r="D5" t="n">
-        <v>22.56</v>
+        <v>37.9</v>
       </c>
       <c r="E5" t="n">
-        <v>22.4027</v>
+        <v>7.7774</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GV_1_f_D0_A</t>
+          <t>GM_1_v_D0_A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.8915</v>
+        <v>26.4259</v>
       </c>
       <c r="C6" t="n">
-        <v>113.31</v>
+        <v>13.57</v>
       </c>
       <c r="D6" t="n">
-        <v>37.9</v>
+        <v>10.94</v>
       </c>
       <c r="E6" t="n">
-        <v>7.7774</v>
+        <v>2.3546</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_A</t>
+          <t>GM_1_f_D0_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.4259</v>
+        <v>13.5196</v>
       </c>
       <c r="C7" t="n">
-        <v>13.57</v>
+        <v>6.67</v>
       </c>
       <c r="D7" t="n">
-        <v>10.94</v>
+        <v>5.21</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3546</v>
+        <v>2.6986</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_B</t>
+          <t>GM_1_v_D0_B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.5196</v>
+        <v>15.0687</v>
       </c>
       <c r="C8" t="n">
-        <v>6.67</v>
+        <v>10.88</v>
       </c>
       <c r="D8" t="n">
-        <v>5.21</v>
+        <v>7.87</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6986</v>
+        <v>2.0181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_B</t>
+          <t>GM_0_f_DM16_A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.0687</v>
+        <v>66.46420000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>10.88</v>
+        <v>28.95</v>
       </c>
       <c r="D9" t="n">
-        <v>7.87</v>
+        <v>20.67</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0181</v>
+        <v>19.037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GM_0_f_DM16_A</t>
+          <t>GM_1_f_DM32_A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66.46420000000001</v>
+        <v>13.6533</v>
       </c>
       <c r="C10" t="n">
-        <v>28.95</v>
+        <v>6.75</v>
       </c>
       <c r="D10" t="n">
-        <v>20.67</v>
+        <v>5.23</v>
       </c>
       <c r="E10" t="n">
-        <v>19.037</v>
+        <v>2.9021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GM_1_f_DM32_A</t>
+          <t>GM_2_f_DV32_A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.6533</v>
+        <v>77.6369</v>
       </c>
       <c r="C11" t="n">
-        <v>6.75</v>
+        <v>35.26</v>
       </c>
       <c r="D11" t="n">
-        <v>5.23</v>
+        <v>22.92</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9021</v>
+        <v>21.1906</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GM_2_f_DV32_A</t>
+          <t>GM_1_v_DV32_A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77.6369</v>
+        <v>31.3938</v>
       </c>
       <c r="C12" t="n">
-        <v>35.26</v>
+        <v>18.02</v>
       </c>
       <c r="D12" t="n">
-        <v>22.92</v>
+        <v>13.49</v>
       </c>
       <c r="E12" t="n">
-        <v>21.1906</v>
+        <v>2.157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GM_1_v_DV32_A</t>
+          <t>GM_2_v_DM16_A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.3938</v>
+        <v>53.6481</v>
       </c>
       <c r="C13" t="n">
-        <v>18.02</v>
+        <v>32.6</v>
       </c>
       <c r="D13" t="n">
-        <v>13.49</v>
+        <v>17.66</v>
       </c>
       <c r="E13" t="n">
-        <v>2.157</v>
+        <v>19.7829</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GM_2_v_DM16_A</t>
+          <t>GM_2+_f_DM16_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53.6481</v>
+        <v>66.31319999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>32.6</v>
+        <v>30.25</v>
       </c>
       <c r="D14" t="n">
-        <v>17.66</v>
+        <v>20.18</v>
       </c>
       <c r="E14" t="n">
-        <v>19.7829</v>
+        <v>20.9682</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GM_2+_f_DM16_A</t>
+          <t>GM_2+_v_DV16_A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66.31319999999999</v>
+        <v>80.6433</v>
       </c>
       <c r="C15" t="n">
-        <v>30.25</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>20.18</v>
+        <v>25.94</v>
       </c>
       <c r="E15" t="n">
-        <v>20.9682</v>
+        <v>31.487</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GM_2+_v_DV16_A</t>
+          <t>BASELINE_BEM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80.6433</v>
+        <v>22.3797</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>17.44</v>
       </c>
       <c r="D16" t="n">
-        <v>25.94</v>
+        <v>9.94</v>
       </c>
       <c r="E16" t="n">
-        <v>31.487</v>
+        <v>13.8425</v>
       </c>
     </row>
   </sheetData>
@@ -1705,286 +1747,286 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BASELINE_BEM</t>
+          <t>GM_0_f_D0_A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1036</v>
+        <v>21.551</v>
       </c>
       <c r="C2" t="n">
-        <v>76.61</v>
+        <v>343.04</v>
       </c>
       <c r="D2" t="n">
-        <v>4.22</v>
+        <v>7.13</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7467</v>
+        <v>11.2589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM_0_f_D0_A</t>
+          <t>GM_1_f_D0_A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.551</v>
+        <v>4.7004</v>
       </c>
       <c r="C3" t="n">
-        <v>343.04</v>
+        <v>60.7</v>
       </c>
       <c r="D3" t="n">
-        <v>7.13</v>
+        <v>3.13</v>
       </c>
       <c r="E3" t="n">
-        <v>11.2589</v>
+        <v>0.9313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_A</t>
+          <t>GM_2_f_D0_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7004</v>
+        <v>21.5891</v>
       </c>
       <c r="C4" t="n">
-        <v>60.7</v>
+        <v>467.41</v>
       </c>
       <c r="D4" t="n">
-        <v>3.13</v>
+        <v>7.19</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9313</v>
+        <v>11.1847</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM_2_f_D0_A</t>
+          <t>GV_1_f_D0_A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.5891</v>
+        <v>7.625</v>
       </c>
       <c r="C5" t="n">
-        <v>467.41</v>
+        <v>131.56</v>
       </c>
       <c r="D5" t="n">
-        <v>7.19</v>
+        <v>10.25</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1847</v>
+        <v>1.879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GV_1_f_D0_A</t>
+          <t>GM_1_v_D0_A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.625</v>
+        <v>6.2058</v>
       </c>
       <c r="C6" t="n">
-        <v>131.56</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>10.25</v>
+        <v>3.83</v>
       </c>
       <c r="E6" t="n">
-        <v>1.879</v>
+        <v>0.6671</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_A</t>
+          <t>GM_1_f_D0_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.2058</v>
+        <v>4.7709</v>
       </c>
       <c r="C7" t="n">
-        <v>73.98999999999999</v>
+        <v>65.17</v>
       </c>
       <c r="D7" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6671</v>
+        <v>0.8798</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_B</t>
+          <t>GM_1_v_D0_B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7709</v>
+        <v>5.3072</v>
       </c>
       <c r="C8" t="n">
-        <v>65.17</v>
+        <v>64.88</v>
       </c>
       <c r="D8" t="n">
-        <v>3.15</v>
+        <v>3.72</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8798</v>
+        <v>0.6574</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_B</t>
+          <t>GM_0_f_DM16_A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3072</v>
+        <v>16.0165</v>
       </c>
       <c r="C9" t="n">
-        <v>64.88</v>
+        <v>519.9</v>
       </c>
       <c r="D9" t="n">
-        <v>3.72</v>
+        <v>6.3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6574</v>
+        <v>7.7832</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GM_0_f_DM16_A</t>
+          <t>GM_1_f_DM32_A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.0165</v>
+        <v>4.847</v>
       </c>
       <c r="C10" t="n">
-        <v>519.9</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>6.3</v>
+        <v>3.21</v>
       </c>
       <c r="E10" t="n">
-        <v>7.7832</v>
+        <v>1.0139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GM_1_f_DM32_A</t>
+          <t>GM_2_f_DV32_A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.847</v>
+        <v>22.7838</v>
       </c>
       <c r="C11" t="n">
-        <v>75.48999999999999</v>
+        <v>550.73</v>
       </c>
       <c r="D11" t="n">
-        <v>3.21</v>
+        <v>7.58</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0139</v>
+        <v>10.6371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GM_2_f_DV32_A</t>
+          <t>GM_1_v_DV32_A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.7838</v>
+        <v>6.3572</v>
       </c>
       <c r="C12" t="n">
-        <v>550.73</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>7.58</v>
+        <v>3.95</v>
       </c>
       <c r="E12" t="n">
-        <v>10.6371</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GM_1_v_DV32_A</t>
+          <t>GM_2_v_DM16_A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.3572</v>
+        <v>14.3137</v>
       </c>
       <c r="C13" t="n">
-        <v>77.54000000000001</v>
+        <v>425</v>
       </c>
       <c r="D13" t="n">
-        <v>3.95</v>
+        <v>6.02</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7153</v>
+        <v>6.5468</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GM_2_v_DM16_A</t>
+          <t>GM_2+_f_DM16_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.3137</v>
+        <v>16.6113</v>
       </c>
       <c r="C14" t="n">
-        <v>425</v>
+        <v>370.98</v>
       </c>
       <c r="D14" t="n">
-        <v>6.02</v>
+        <v>7.42</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5468</v>
+        <v>5.0356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GM_2+_f_DM16_A</t>
+          <t>GM_2+_v_DV16_A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.6113</v>
+        <v>20.926</v>
       </c>
       <c r="C15" t="n">
-        <v>370.98</v>
+        <v>255.04</v>
       </c>
       <c r="D15" t="n">
-        <v>7.42</v>
+        <v>7.47</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0356</v>
+        <v>9.324400000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GM_2+_v_DV16_A</t>
+          <t>BASELINE_BEM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.926</v>
+        <v>6.1036</v>
       </c>
       <c r="C16" t="n">
-        <v>255.04</v>
+        <v>76.61</v>
       </c>
       <c r="D16" t="n">
-        <v>7.47</v>
+        <v>4.22</v>
       </c>
       <c r="E16" t="n">
-        <v>9.324400000000001</v>
+        <v>2.7467</v>
       </c>
     </row>
   </sheetData>
@@ -2026,241 +2068,241 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BASELINE_BEM</t>
+          <t>GM_0_f_D0_A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.100939</v>
+        <v>0.369222</v>
       </c>
       <c r="C2" t="n">
-        <v>27.84</v>
+        <v>113.39</v>
       </c>
       <c r="D2" t="n">
-        <v>0.082235</v>
+        <v>0.230921</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM_0_f_D0_A</t>
+          <t>GM_1_f_D0_A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.369222</v>
+        <v>0.023751</v>
       </c>
       <c r="C3" t="n">
-        <v>113.39</v>
+        <v>6.74</v>
       </c>
       <c r="D3" t="n">
-        <v>0.230921</v>
+        <v>0.009035</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_A</t>
+          <t>GM_2_f_D0_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.023751</v>
+        <v>0.540672</v>
       </c>
       <c r="C4" t="n">
-        <v>6.74</v>
+        <v>166.03</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009035</v>
+        <v>0.337926</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM_2_f_D0_A</t>
+          <t>GV_1_f_D0_A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.540672</v>
+        <v>0.044846</v>
       </c>
       <c r="C5" t="n">
-        <v>166.03</v>
+        <v>11.93</v>
       </c>
       <c r="D5" t="n">
-        <v>0.337926</v>
+        <v>0.037763</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GV_1_f_D0_A</t>
+          <t>GM_1_v_D0_A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.044846</v>
+        <v>0.021267</v>
       </c>
       <c r="C6" t="n">
-        <v>11.93</v>
+        <v>5.92</v>
       </c>
       <c r="D6" t="n">
-        <v>0.037763</v>
+        <v>0.011236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_A</t>
+          <t>GM_1_f_D0_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.021267</v>
+        <v>0.029848</v>
       </c>
       <c r="C7" t="n">
-        <v>5.92</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.011236</v>
+        <v>0.011884</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_B</t>
+          <t>GM_1_v_D0_B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.029848</v>
+        <v>0.016841</v>
       </c>
       <c r="C8" t="n">
-        <v>8.960000000000001</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.011884</v>
+        <v>0.011199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_B</t>
+          <t>GM_0_f_DM16_A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.016841</v>
+        <v>0.563019</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>173.64</v>
       </c>
       <c r="D9" t="n">
-        <v>0.011199</v>
+        <v>0.320166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GM_0_f_DM16_A</t>
+          <t>GM_1_f_DM32_A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.563019</v>
+        <v>0.037671</v>
       </c>
       <c r="C10" t="n">
-        <v>173.64</v>
+        <v>11.66</v>
       </c>
       <c r="D10" t="n">
-        <v>0.320166</v>
+        <v>0.017383</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GM_1_f_DM32_A</t>
+          <t>GM_2_f_DV32_A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.037671</v>
+        <v>0.62121</v>
       </c>
       <c r="C11" t="n">
-        <v>11.66</v>
+        <v>191.15</v>
       </c>
       <c r="D11" t="n">
-        <v>0.017383</v>
+        <v>0.386526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GM_2_f_DV32_A</t>
+          <t>GM_1_v_DV32_A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.62121</v>
+        <v>0.013115</v>
       </c>
       <c r="C12" t="n">
-        <v>191.15</v>
+        <v>3.65</v>
       </c>
       <c r="D12" t="n">
-        <v>0.386526</v>
+        <v>0.007293</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GM_1_v_DV32_A</t>
+          <t>GM_2_v_DM16_A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.013115</v>
+        <v>0.450615</v>
       </c>
       <c r="C13" t="n">
-        <v>3.65</v>
+        <v>140.58</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007293</v>
+        <v>0.230018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GM_2_v_DM16_A</t>
+          <t>GM_2+_f_DM16_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.450615</v>
+        <v>0.371489</v>
       </c>
       <c r="C14" t="n">
-        <v>140.58</v>
+        <v>116.08</v>
       </c>
       <c r="D14" t="n">
-        <v>0.230018</v>
+        <v>0.186534</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GM_2+_f_DM16_A</t>
+          <t>GM_2+_v_DV16_A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.371489</v>
+        <v>0.2011</v>
       </c>
       <c r="C15" t="n">
-        <v>116.08</v>
+        <v>56.05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.186534</v>
+        <v>0.14312</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GM_2+_v_DV16_A</t>
+          <t>BASELINE_BEM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2011</v>
+        <v>0.100939</v>
       </c>
       <c r="C16" t="n">
-        <v>56.05</v>
+        <v>27.84</v>
       </c>
       <c r="D16" t="n">
-        <v>0.14312</v>
+        <v>0.082235</v>
       </c>
     </row>
   </sheetData>
@@ -2302,241 +2344,241 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BASELINE_BEM</t>
+          <t>GM_0_f_D0_A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.105264</v>
+        <v>0.243753</v>
       </c>
       <c r="C2" t="n">
-        <v>9.640000000000001</v>
+        <v>24.36</v>
       </c>
       <c r="D2" t="n">
-        <v>0.082014</v>
+        <v>0.188867</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM_0_f_D0_A</t>
+          <t>GM_1_f_D0_A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.243753</v>
+        <v>0.029351</v>
       </c>
       <c r="C3" t="n">
-        <v>24.36</v>
+        <v>2.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.188867</v>
+        <v>0.020692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_A</t>
+          <t>GM_2_f_D0_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.029351</v>
+        <v>0.307363</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9</v>
+        <v>30.18</v>
       </c>
       <c r="D4" t="n">
-        <v>0.020692</v>
+        <v>0.236662</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM_2_f_D0_A</t>
+          <t>GV_1_f_D0_A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.307363</v>
+        <v>0.04927</v>
       </c>
       <c r="C5" t="n">
-        <v>30.18</v>
+        <v>4.54</v>
       </c>
       <c r="D5" t="n">
-        <v>0.236662</v>
+        <v>0.035335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GV_1_f_D0_A</t>
+          <t>GM_1_v_D0_A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04927</v>
+        <v>0.026826</v>
       </c>
       <c r="C6" t="n">
-        <v>4.54</v>
+        <v>2.91</v>
       </c>
       <c r="D6" t="n">
-        <v>0.035335</v>
+        <v>0.016729</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_A</t>
+          <t>GM_1_f_D0_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.026826</v>
+        <v>0.031807</v>
       </c>
       <c r="C7" t="n">
-        <v>2.91</v>
+        <v>3.47</v>
       </c>
       <c r="D7" t="n">
-        <v>0.016729</v>
+        <v>0.023857</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_B</t>
+          <t>GM_1_v_D0_B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.031807</v>
+        <v>0.023998</v>
       </c>
       <c r="C8" t="n">
-        <v>3.47</v>
+        <v>2.37</v>
       </c>
       <c r="D8" t="n">
-        <v>0.023857</v>
+        <v>0.016896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_B</t>
+          <t>GM_0_f_DM16_A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.023998</v>
+        <v>0.257345</v>
       </c>
       <c r="C9" t="n">
-        <v>2.37</v>
+        <v>24.99</v>
       </c>
       <c r="D9" t="n">
-        <v>0.016896</v>
+        <v>0.193551</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GM_0_f_DM16_A</t>
+          <t>GM_1_f_DM32_A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.257345</v>
+        <v>0.026712</v>
       </c>
       <c r="C10" t="n">
-        <v>24.99</v>
+        <v>3.19</v>
       </c>
       <c r="D10" t="n">
-        <v>0.193551</v>
+        <v>0.019115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GM_1_f_DM32_A</t>
+          <t>GM_2_f_DV32_A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.026712</v>
+        <v>0.344392</v>
       </c>
       <c r="C11" t="n">
-        <v>3.19</v>
+        <v>32.31</v>
       </c>
       <c r="D11" t="n">
-        <v>0.019115</v>
+        <v>0.254288</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GM_2_f_DV32_A</t>
+          <t>GM_1_v_DV32_A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.344392</v>
+        <v>0.019314</v>
       </c>
       <c r="C12" t="n">
-        <v>32.31</v>
+        <v>1.82</v>
       </c>
       <c r="D12" t="n">
-        <v>0.254288</v>
+        <v>0.011831</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GM_1_v_DV32_A</t>
+          <t>GM_2_v_DM16_A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.019314</v>
+        <v>0.311169</v>
       </c>
       <c r="C13" t="n">
-        <v>1.82</v>
+        <v>26.71</v>
       </c>
       <c r="D13" t="n">
-        <v>0.011831</v>
+        <v>0.190001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GM_2_v_DM16_A</t>
+          <t>GM_2+_f_DM16_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.311169</v>
+        <v>0.279345</v>
       </c>
       <c r="C14" t="n">
-        <v>26.71</v>
+        <v>24.92</v>
       </c>
       <c r="D14" t="n">
-        <v>0.190001</v>
+        <v>0.186177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GM_2+_f_DM16_A</t>
+          <t>GM_2+_v_DV16_A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.279345</v>
+        <v>0.232965</v>
       </c>
       <c r="C15" t="n">
-        <v>24.92</v>
+        <v>23.78</v>
       </c>
       <c r="D15" t="n">
-        <v>0.186177</v>
+        <v>0.15649</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GM_2+_v_DV16_A</t>
+          <t>BASELINE_BEM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.232965</v>
+        <v>0.105264</v>
       </c>
       <c r="C16" t="n">
-        <v>23.78</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.15649</v>
+        <v>0.082014</v>
       </c>
     </row>
   </sheetData>
@@ -2583,286 +2625,286 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BASELINE_BEM</t>
+          <t>GM_0_f_D0_A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.05</v>
+        <v>370.78</v>
       </c>
       <c r="C2" t="n">
-        <v>14.16</v>
+        <v>27.2</v>
       </c>
       <c r="D2" t="n">
-        <v>37.48</v>
+        <v>137.76</v>
       </c>
       <c r="E2" t="n">
-        <v>8.292199999999999</v>
+        <v>15.4773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM_0_f_D0_A</t>
+          <t>GM_1_f_D0_A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>370.78</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>27.2</v>
+        <v>8.07</v>
       </c>
       <c r="D3" t="n">
-        <v>137.76</v>
+        <v>9.65</v>
       </c>
       <c r="E3" t="n">
-        <v>15.4773</v>
+        <v>1.6832</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_A</t>
+          <t>GM_2_f_D0_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67.20999999999999</v>
+        <v>499.5</v>
       </c>
       <c r="C4" t="n">
-        <v>8.07</v>
+        <v>29.75</v>
       </c>
       <c r="D4" t="n">
-        <v>9.65</v>
+        <v>196.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6832</v>
+        <v>16.7398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM_2_f_D0_A</t>
+          <t>GV_1_f_D0_A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>499.5</v>
+        <v>244.87</v>
       </c>
       <c r="C5" t="n">
-        <v>29.75</v>
+        <v>48.15</v>
       </c>
       <c r="D5" t="n">
-        <v>196.2</v>
+        <v>16.47</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7398</v>
+        <v>4.5997</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GV_1_f_D0_A</t>
+          <t>GM_1_v_D0_A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>244.87</v>
+        <v>87.56</v>
       </c>
       <c r="C6" t="n">
-        <v>48.15</v>
+        <v>14.77</v>
       </c>
       <c r="D6" t="n">
-        <v>16.47</v>
+        <v>8.83</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5997</v>
+        <v>1.5104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_A</t>
+          <t>GM_1_f_D0_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87.56</v>
+        <v>71.83</v>
       </c>
       <c r="C7" t="n">
-        <v>14.77</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>8.83</v>
+        <v>12.43</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5104</v>
+        <v>1.7682</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GM_1_f_D0_B</t>
+          <t>GM_1_v_D0_B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71.83</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>8.369999999999999</v>
+        <v>11.59</v>
       </c>
       <c r="D8" t="n">
-        <v>12.43</v>
+        <v>7.37</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7682</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GM_1_v_D0_B</t>
+          <t>GM_0_f_DM16_A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75.76000000000001</v>
+        <v>548.85</v>
       </c>
       <c r="C9" t="n">
-        <v>11.59</v>
+        <v>26.98</v>
       </c>
       <c r="D9" t="n">
-        <v>7.37</v>
+        <v>198.63</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3219</v>
+        <v>13.3758</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GM_0_f_DM16_A</t>
+          <t>GM_1_f_DM32_A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>548.85</v>
+        <v>82.23</v>
       </c>
       <c r="C10" t="n">
-        <v>26.98</v>
+        <v>8.44</v>
       </c>
       <c r="D10" t="n">
-        <v>198.63</v>
+        <v>14.85</v>
       </c>
       <c r="E10" t="n">
-        <v>13.3758</v>
+        <v>1.9378</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GM_1_f_DM32_A</t>
+          <t>GM_2_f_DV32_A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82.23</v>
+        <v>585.98</v>
       </c>
       <c r="C11" t="n">
-        <v>8.44</v>
+        <v>30.5</v>
       </c>
       <c r="D11" t="n">
-        <v>14.85</v>
+        <v>223.46</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9378</v>
+        <v>15.8627</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GM_2_f_DV32_A</t>
+          <t>GM_1_v_DV32_A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>585.98</v>
+        <v>95.56</v>
       </c>
       <c r="C12" t="n">
-        <v>30.5</v>
+        <v>17.44</v>
       </c>
       <c r="D12" t="n">
-        <v>223.46</v>
+        <v>5.47</v>
       </c>
       <c r="E12" t="n">
-        <v>15.8627</v>
+        <v>1.4156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GM_1_v_DV32_A</t>
+          <t>GM_2_v_DM16_A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>95.56</v>
+        <v>457.61</v>
       </c>
       <c r="C13" t="n">
-        <v>17.44</v>
+        <v>23.68</v>
       </c>
       <c r="D13" t="n">
-        <v>5.47</v>
+        <v>167.29</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4156</v>
+        <v>13.1408</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GM_2_v_DM16_A</t>
+          <t>GM_2+_f_DM16_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>457.61</v>
+        <v>401.23</v>
       </c>
       <c r="C14" t="n">
-        <v>23.68</v>
+        <v>27.6</v>
       </c>
       <c r="D14" t="n">
-        <v>167.29</v>
+        <v>141</v>
       </c>
       <c r="E14" t="n">
-        <v>13.1408</v>
+        <v>12.9736</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GM_2+_f_DM16_A</t>
+          <t>GM_2+_v_DV16_A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401.23</v>
+        <v>293.04</v>
       </c>
       <c r="C15" t="n">
-        <v>27.6</v>
+        <v>33.41</v>
       </c>
       <c r="D15" t="n">
-        <v>141</v>
+        <v>79.83</v>
       </c>
       <c r="E15" t="n">
-        <v>12.9736</v>
+        <v>19.3422</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GM_2+_v_DV16_A</t>
+          <t>BASELINE_BEM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>293.04</v>
+        <v>94.05</v>
       </c>
       <c r="C16" t="n">
-        <v>33.41</v>
+        <v>14.16</v>
       </c>
       <c r="D16" t="n">
-        <v>79.83</v>
+        <v>37.48</v>
       </c>
       <c r="E16" t="n">
-        <v>19.3422</v>
+        <v>8.292199999999999</v>
       </c>
     </row>
   </sheetData>
